--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/CONNECTICUT_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/CONNECTICUT_2013.xlsx
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C277">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C563">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C610">
